--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_mp_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_mp_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>30-04-2021 08:30</t>
+          <t>2021-04-30 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>20-05-2021 08:30</t>
+          <t>2021-05-20 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>15-10-2021 08:30</t>
+          <t>2021-10-15 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>31-12-2021 08:30</t>
+          <t>2021-12-31 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4370,7 +4370,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>30-04-2021 08:30</t>
+          <t>2021-04-30 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>23-01-2021 08:30</t>
+          <t>2021-01-23 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9535,7 +9535,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>03-07-2021 08:30</t>
+          <t>2021-03-07 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>07-11-2021 08:30</t>
+          <t>2021-07-11 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10105,7 +10105,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="inlineStr"/>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="n">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12177,7 +12177,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>28-02-2021 08:30</t>
+          <t>2021-02-28 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12549,7 +12549,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr"/>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr"/>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="inlineStr"/>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14536,7 +14536,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15573,7 +15573,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -15949,7 +15949,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18095,7 +18095,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18194,7 +18194,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -18689,7 +18689,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -18891,7 +18891,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="n">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19390,7 +19390,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="inlineStr"/>
@@ -19788,7 +19788,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="n">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="n">
@@ -20089,7 +20089,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="n">
@@ -20192,7 +20192,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="n">
@@ -20295,7 +20295,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="n">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="n">
@@ -20497,7 +20497,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="n">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="n">
@@ -20703,7 +20703,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="n">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="n">
@@ -20909,7 +20909,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="n">
@@ -21004,7 +21004,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="n">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="n">
@@ -21194,7 +21194,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="n">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="n">
@@ -21384,7 +21384,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="n">
@@ -21479,7 +21479,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="n">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="n">
@@ -21669,7 +21669,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="n">
@@ -21764,7 +21764,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="n">
@@ -21859,7 +21859,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="n">
@@ -21954,7 +21954,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="n">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -22142,7 +22142,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="inlineStr"/>
@@ -22235,7 +22235,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="inlineStr"/>
@@ -22328,7 +22328,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
@@ -22421,7 +22421,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="inlineStr"/>
@@ -22514,7 +22514,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -22607,7 +22607,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22793,7 +22793,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -22979,7 +22979,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -23072,7 +23072,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -23165,7 +23165,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23258,7 +23258,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23351,7 +23351,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr"/>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="n">
@@ -23824,7 +23824,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="n">
@@ -23919,7 +23919,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>25-08-2021 08:30</t>
+          <t>2021-08-25 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="n">
@@ -24014,7 +24014,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>27-09-2021 08:30</t>
+          <t>2021-09-27 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="n">
@@ -24109,7 +24109,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="n">
@@ -24204,7 +24204,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="n">
@@ -24299,7 +24299,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="n">
@@ -24394,7 +24394,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr"/>
@@ -24487,7 +24487,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="inlineStr"/>
@@ -24580,7 +24580,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="inlineStr"/>
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -24768,7 +24768,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="inlineStr"/>
@@ -24956,7 +24956,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -25051,7 +25051,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>14-09-2021 08:30</t>
+          <t>2021-09-14 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -25146,7 +25146,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -25336,7 +25336,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="n">
@@ -25431,7 +25431,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="inlineStr"/>
@@ -25524,7 +25524,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="inlineStr"/>
@@ -25617,7 +25617,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="inlineStr"/>
@@ -25710,7 +25710,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="n">
@@ -25805,7 +25805,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="n">
@@ -25900,7 +25900,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="n">
@@ -25995,7 +25995,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>25-04-2021 08:30</t>
+          <t>2021-04-25 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="n">
@@ -26090,7 +26090,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>14-05-2021 08:30</t>
+          <t>2021-05-14 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="n">
@@ -26185,7 +26185,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>13-06-2021 08:30</t>
+          <t>2021-06-13 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="n">
@@ -26280,7 +26280,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>16-07-2021 08:30</t>
+          <t>2021-07-16 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="n">
@@ -26375,7 +26375,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>08-08-2021 08:30</t>
+          <t>2021-08-08 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="n">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="n">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="n">
@@ -26755,7 +26755,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="n">
@@ -26850,7 +26850,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="inlineStr"/>
@@ -26943,7 +26943,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="inlineStr"/>
@@ -27036,7 +27036,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="inlineStr"/>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="inlineStr"/>
@@ -27222,7 +27222,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="inlineStr"/>
@@ -27315,7 +27315,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="inlineStr"/>
@@ -27408,7 +27408,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="inlineStr"/>
@@ -27501,7 +27501,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="inlineStr"/>
@@ -27594,7 +27594,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="n">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="n">
@@ -27784,7 +27784,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="n">
@@ -27879,7 +27879,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="n">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="n">
@@ -28069,7 +28069,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="n">
@@ -28164,7 +28164,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="n">
@@ -28259,7 +28259,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="n">
@@ -28354,7 +28354,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="n">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="n">
@@ -28544,7 +28544,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="inlineStr"/>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="inlineStr"/>
@@ -28730,7 +28730,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="inlineStr"/>
@@ -28823,7 +28823,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="inlineStr"/>
@@ -28916,7 +28916,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="inlineStr"/>
@@ -29009,7 +29009,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="inlineStr"/>
@@ -29102,7 +29102,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="inlineStr"/>
@@ -29195,7 +29195,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="inlineStr"/>
@@ -29288,7 +29288,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="inlineStr"/>
@@ -29381,7 +29381,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="n">
@@ -29476,7 +29476,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="n">
@@ -29571,7 +29571,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="n">
@@ -29666,7 +29666,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="n">
@@ -29761,7 +29761,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="n">
@@ -29856,7 +29856,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="n">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="n">
@@ -30046,7 +30046,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="n">
@@ -30141,7 +30141,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="n">
@@ -30236,7 +30236,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="n">
@@ -30331,7 +30331,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="n">
@@ -30426,7 +30426,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="n">
@@ -30521,7 +30521,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="inlineStr"/>
@@ -30707,7 +30707,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="inlineStr"/>
@@ -30800,7 +30800,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="n">
@@ -30895,7 +30895,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="n">
@@ -30990,7 +30990,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="n">
@@ -31085,7 +31085,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>28-04-2021 08:30</t>
+          <t>2021-04-28 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="n">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>28-05-2021 08:30</t>
+          <t>2021-05-28 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="n">
@@ -31275,7 +31275,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>23-06-2021 08:30</t>
+          <t>2021-06-23 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="n">
@@ -31370,7 +31370,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>23-07-2021 08:30</t>
+          <t>2021-07-23 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="n">
@@ -31465,7 +31465,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="n">
@@ -31560,7 +31560,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>24-09-2021 08:30</t>
+          <t>2021-09-24 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="n">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>23-10-2021 08:30</t>
+          <t>2021-10-23 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="n">
@@ -31750,7 +31750,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="n">
@@ -31845,7 +31845,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="n">
@@ -31940,7 +31940,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="inlineStr"/>
@@ -32033,7 +32033,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="inlineStr"/>
@@ -32126,7 +32126,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="inlineStr"/>
@@ -32219,7 +32219,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="inlineStr"/>
@@ -32312,7 +32312,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="inlineStr"/>
@@ -32405,7 +32405,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32498,7 +32498,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="inlineStr"/>
@@ -32591,7 +32591,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="inlineStr"/>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="inlineStr"/>
@@ -32777,7 +32777,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="inlineStr"/>
@@ -32963,7 +32963,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="inlineStr"/>
@@ -33056,7 +33056,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -33149,7 +33149,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -33242,7 +33242,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -33335,7 +33335,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="inlineStr"/>
@@ -33428,7 +33428,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -33521,7 +33521,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="inlineStr"/>
@@ -33614,7 +33614,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -33707,7 +33707,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>28-02-2021 08:30</t>
+          <t>2021-02-28 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -33800,7 +33800,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="inlineStr"/>
@@ -33893,7 +33893,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="n">
@@ -33988,7 +33988,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="n">
@@ -34083,7 +34083,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="n">
@@ -34178,7 +34178,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="n">
@@ -34273,7 +34273,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="n">
@@ -34368,7 +34368,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="n">
@@ -34463,7 +34463,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="n">
@@ -34558,7 +34558,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>29-09-2021 08:30</t>
+          <t>2021-09-29 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -34653,7 +34653,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="n">
@@ -34748,7 +34748,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="n">
@@ -34843,7 +34843,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="n">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="n">
@@ -35033,7 +35033,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="n">
@@ -35128,7 +35128,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="n">
@@ -35223,7 +35223,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>04-04-2021 08:30</t>
+          <t>2021-04-04 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="n">
@@ -35318,7 +35318,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>24-05-2021 08:30</t>
+          <t>2021-05-24 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="n">
@@ -35413,7 +35413,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>16-06-2021 08:30</t>
+          <t>2021-06-16 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="n">
@@ -35508,7 +35508,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>01-07-2021 08:30</t>
+          <t>2021-01-07 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="n">
@@ -35603,7 +35603,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="n">
@@ -35698,7 +35698,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="n">
@@ -35793,7 +35793,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="n">
@@ -35888,7 +35888,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="n">
@@ -35983,7 +35983,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="n">
@@ -36078,7 +36078,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="inlineStr"/>
@@ -36171,7 +36171,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="inlineStr"/>
@@ -36357,7 +36357,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="inlineStr"/>
@@ -36450,7 +36450,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="inlineStr"/>
@@ -36543,7 +36543,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="inlineStr"/>
@@ -36636,7 +36636,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="inlineStr"/>
@@ -36729,7 +36729,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="inlineStr"/>
@@ -36822,7 +36822,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="inlineStr"/>
@@ -36915,7 +36915,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="inlineStr"/>
@@ -37008,7 +37008,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="inlineStr"/>
@@ -37101,7 +37101,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="inlineStr"/>
@@ -37194,7 +37194,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="inlineStr"/>
@@ -37287,7 +37287,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="inlineStr"/>
@@ -37380,7 +37380,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="n">
@@ -37475,7 +37475,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="n">
@@ -37570,7 +37570,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="n">
@@ -37665,7 +37665,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>18-05-2021 08:30</t>
+          <t>2021-05-18 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="n">
@@ -37760,7 +37760,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>17-09-2021 08:30</t>
+          <t>2021-09-17 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="n">
@@ -37855,7 +37855,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="n">
@@ -37950,7 +37950,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="n">
@@ -38045,7 +38045,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="n">
@@ -38140,7 +38140,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="n">
@@ -38235,7 +38235,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="n">
@@ -38330,7 +38330,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="n">
@@ -38425,7 +38425,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="n">
@@ -38520,7 +38520,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="n">
@@ -38615,7 +38615,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="n">
@@ -38710,7 +38710,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="n">
@@ -38805,7 +38805,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="n">
@@ -38900,7 +38900,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="n">
@@ -38995,7 +38995,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="n">
@@ -39090,7 +39090,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="n">
@@ -39185,7 +39185,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="n">
@@ -39280,7 +39280,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="n">
@@ -39375,7 +39375,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="n">
@@ -39470,7 +39470,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="n">
@@ -39565,7 +39565,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="n">
@@ -39660,7 +39660,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>16-05-2021 08:30</t>
+          <t>2021-05-16 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="n">
@@ -39755,7 +39755,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>12-06-2021 08:30</t>
+          <t>2021-12-06 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="n">
@@ -39850,7 +39850,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>18-07-2021 08:30</t>
+          <t>2021-07-18 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="n">
@@ -39945,7 +39945,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="n">
@@ -40040,7 +40040,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>05-09-2021 08:30</t>
+          <t>2021-05-09 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="n">
@@ -40135,7 +40135,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="n">
@@ -40230,7 +40230,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="n">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="n">
@@ -40420,7 +40420,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="n">
@@ -40515,7 +40515,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="n">
@@ -40610,7 +40610,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>31-03-2021 08:30</t>
+          <t>2021-03-31 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="n">
@@ -40705,7 +40705,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="n">
@@ -40800,7 +40800,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="n">
@@ -40895,7 +40895,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="n">
@@ -40990,7 +40990,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="n">
@@ -41085,7 +41085,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>14-08-2021 08:30</t>
+          <t>2021-08-14 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="n">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="n">
@@ -41275,7 +41275,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="n">
@@ -41370,7 +41370,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="n">
@@ -41465,7 +41465,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="n">
@@ -41560,7 +41560,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="inlineStr"/>
@@ -41653,7 +41653,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="inlineStr"/>
@@ -41746,7 +41746,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="inlineStr"/>
@@ -41839,7 +41839,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="inlineStr"/>
@@ -41932,7 +41932,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="inlineStr"/>
@@ -42025,7 +42025,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="inlineStr"/>
@@ -42118,7 +42118,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="inlineStr"/>
@@ -42211,7 +42211,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="inlineStr"/>
@@ -42304,7 +42304,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="inlineStr"/>
@@ -42397,7 +42397,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="inlineStr"/>
@@ -42490,7 +42490,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="inlineStr"/>
@@ -42583,7 +42583,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="inlineStr"/>
@@ -42676,7 +42676,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="inlineStr"/>
@@ -42769,7 +42769,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="inlineStr"/>
@@ -42862,7 +42862,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="inlineStr"/>
@@ -42955,7 +42955,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="inlineStr"/>
@@ -43048,7 +43048,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="inlineStr"/>
@@ -43141,7 +43141,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="inlineStr"/>
@@ -43234,7 +43234,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="inlineStr"/>
@@ -43327,7 +43327,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="inlineStr"/>
@@ -43420,7 +43420,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="inlineStr"/>
@@ -43513,7 +43513,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="inlineStr"/>
@@ -43606,7 +43606,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="inlineStr"/>
@@ -43699,7 +43699,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="inlineStr"/>
@@ -43792,7 +43792,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="inlineStr"/>
@@ -43885,7 +43885,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="inlineStr"/>
@@ -43978,7 +43978,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="inlineStr"/>
@@ -44071,7 +44071,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>17-01-2021 08:30</t>
+          <t>2021-01-17 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="inlineStr"/>
@@ -44164,7 +44164,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="inlineStr"/>
@@ -44257,7 +44257,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="inlineStr"/>
@@ -44350,7 +44350,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="inlineStr"/>
@@ -44443,7 +44443,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="inlineStr"/>
@@ -44536,7 +44536,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="inlineStr"/>
@@ -44629,7 +44629,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="inlineStr"/>
@@ -44722,7 +44722,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="inlineStr"/>
@@ -44815,7 +44815,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="inlineStr"/>
@@ -44908,7 +44908,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="inlineStr"/>
@@ -45001,7 +45001,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="inlineStr"/>
@@ -45094,7 +45094,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="inlineStr"/>
@@ -45187,7 +45187,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="inlineStr"/>
@@ -45280,7 +45280,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="inlineStr"/>
@@ -45373,7 +45373,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="inlineStr"/>
@@ -45466,7 +45466,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="inlineStr"/>
@@ -45559,7 +45559,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="inlineStr"/>
@@ -45652,7 +45652,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="inlineStr"/>
@@ -45745,7 +45745,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="inlineStr"/>
@@ -45838,7 +45838,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="inlineStr"/>
@@ -45931,7 +45931,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T481" t="inlineStr"/>
@@ -46024,7 +46024,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T482" t="inlineStr"/>
@@ -46117,7 +46117,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T483" t="inlineStr"/>
@@ -46210,7 +46210,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T484" t="inlineStr"/>
@@ -46303,7 +46303,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T485" t="inlineStr"/>
@@ -46396,7 +46396,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T486" t="inlineStr"/>
@@ -46489,7 +46489,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T487" t="inlineStr"/>
@@ -46582,7 +46582,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T488" t="inlineStr"/>
@@ -46675,7 +46675,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T489" t="inlineStr"/>
@@ -46768,7 +46768,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T490" t="inlineStr"/>
@@ -46861,7 +46861,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T491" t="inlineStr"/>
@@ -46954,7 +46954,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T492" t="inlineStr"/>
@@ -47047,7 +47047,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T493" t="inlineStr"/>
@@ -47140,7 +47140,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T494" t="inlineStr"/>
@@ -47233,7 +47233,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T495" t="inlineStr"/>
@@ -47326,7 +47326,7 @@
       </c>
       <c r="S496" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T496" t="inlineStr"/>
@@ -47419,7 +47419,7 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T497" t="inlineStr"/>
@@ -47512,7 +47512,7 @@
       </c>
       <c r="S498" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T498" t="inlineStr"/>
@@ -47605,7 +47605,7 @@
       </c>
       <c r="S499" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T499" t="inlineStr"/>
@@ -47698,7 +47698,7 @@
       </c>
       <c r="S500" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T500" t="inlineStr"/>
@@ -47791,7 +47791,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T501" t="inlineStr"/>
@@ -47884,7 +47884,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T502" t="inlineStr"/>
@@ -47977,7 +47977,7 @@
       </c>
       <c r="S503" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T503" t="inlineStr"/>
@@ -48070,7 +48070,7 @@
       </c>
       <c r="S504" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T504" t="inlineStr"/>
@@ -48163,7 +48163,7 @@
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T505" t="inlineStr"/>
@@ -48256,7 +48256,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T506" t="inlineStr"/>
@@ -48349,7 +48349,7 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T507" t="inlineStr"/>
@@ -48442,7 +48442,7 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T508" t="inlineStr"/>
@@ -48535,7 +48535,7 @@
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T509" t="inlineStr"/>
@@ -48628,7 +48628,7 @@
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T510" t="inlineStr"/>
@@ -48721,7 +48721,7 @@
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T511" t="inlineStr"/>
@@ -48814,7 +48814,7 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T512" t="inlineStr"/>
@@ -48907,7 +48907,7 @@
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T513" t="inlineStr"/>
@@ -49000,7 +49000,7 @@
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T514" t="inlineStr"/>
@@ -49093,7 +49093,7 @@
       </c>
       <c r="S515" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T515" t="inlineStr"/>
@@ -49186,7 +49186,7 @@
       </c>
       <c r="S516" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T516" t="inlineStr"/>
@@ -49279,7 +49279,7 @@
       </c>
       <c r="S517" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T517" t="inlineStr"/>
@@ -49372,7 +49372,7 @@
       </c>
       <c r="S518" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T518" t="inlineStr"/>
@@ -49465,7 +49465,7 @@
       </c>
       <c r="S519" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T519" t="inlineStr"/>
@@ -49558,7 +49558,7 @@
       </c>
       <c r="S520" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T520" t="inlineStr"/>
@@ -49651,7 +49651,7 @@
       </c>
       <c r="S521" t="inlineStr">
         <is>
-          <t>17-01-2021 08:30</t>
+          <t>2021-01-17 08:30:00</t>
         </is>
       </c>
       <c r="T521" t="inlineStr"/>
@@ -49744,7 +49744,7 @@
       </c>
       <c r="S522" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T522" t="inlineStr"/>
@@ -49837,7 +49837,7 @@
       </c>
       <c r="S523" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T523" t="inlineStr"/>
@@ -49930,7 +49930,7 @@
       </c>
       <c r="S524" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T524" t="inlineStr"/>
@@ -50023,7 +50023,7 @@
       </c>
       <c r="S525" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T525" t="inlineStr"/>
@@ -50116,7 +50116,7 @@
       </c>
       <c r="S526" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T526" t="inlineStr"/>
@@ -50209,7 +50209,7 @@
       </c>
       <c r="S527" t="inlineStr">
         <is>
-          <t>17-01-2021 08:30</t>
+          <t>2021-01-17 08:30:00</t>
         </is>
       </c>
       <c r="T527" t="inlineStr"/>
@@ -50302,7 +50302,7 @@
       </c>
       <c r="S528" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T528" t="inlineStr"/>
@@ -50395,7 +50395,7 @@
       </c>
       <c r="S529" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T529" t="inlineStr"/>
@@ -50488,7 +50488,7 @@
       </c>
       <c r="S530" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T530" t="inlineStr"/>
@@ -50581,7 +50581,7 @@
       </c>
       <c r="S531" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T531" t="inlineStr"/>
@@ -50674,7 +50674,7 @@
       </c>
       <c r="S532" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T532" t="inlineStr"/>
@@ -50767,7 +50767,7 @@
       </c>
       <c r="S533" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T533" t="inlineStr"/>
@@ -50860,7 +50860,7 @@
       </c>
       <c r="S534" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T534" t="inlineStr"/>
@@ -50953,7 +50953,7 @@
       </c>
       <c r="S535" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T535" t="inlineStr"/>
@@ -51046,7 +51046,7 @@
       </c>
       <c r="S536" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T536" t="inlineStr"/>
@@ -51139,7 +51139,7 @@
       </c>
       <c r="S537" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T537" t="inlineStr"/>
@@ -51232,7 +51232,7 @@
       </c>
       <c r="S538" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T538" t="inlineStr"/>
@@ -51325,7 +51325,7 @@
       </c>
       <c r="S539" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T539" t="inlineStr"/>
@@ -51418,7 +51418,7 @@
       </c>
       <c r="S540" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T540" t="inlineStr"/>
@@ -51511,7 +51511,7 @@
       </c>
       <c r="S541" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T541" t="inlineStr"/>
@@ -51604,7 +51604,7 @@
       </c>
       <c r="S542" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T542" t="inlineStr"/>
@@ -51697,7 +51697,7 @@
       </c>
       <c r="S543" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T543" t="inlineStr"/>
@@ -51790,7 +51790,7 @@
       </c>
       <c r="S544" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T544" t="inlineStr"/>
@@ -51883,7 +51883,7 @@
       </c>
       <c r="S545" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T545" t="inlineStr"/>
@@ -51976,7 +51976,7 @@
       </c>
       <c r="S546" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T546" t="inlineStr"/>
@@ -52069,7 +52069,7 @@
       </c>
       <c r="S547" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T547" t="inlineStr"/>
@@ -52162,7 +52162,7 @@
       </c>
       <c r="S548" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T548" t="inlineStr"/>
@@ -52255,7 +52255,7 @@
       </c>
       <c r="S549" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T549" t="inlineStr"/>
@@ -52348,7 +52348,7 @@
       </c>
       <c r="S550" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T550" t="inlineStr"/>
@@ -52441,7 +52441,7 @@
       </c>
       <c r="S551" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T551" t="inlineStr"/>
@@ -52534,7 +52534,7 @@
       </c>
       <c r="S552" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T552" t="inlineStr"/>
@@ -52627,7 +52627,7 @@
       </c>
       <c r="S553" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T553" t="inlineStr"/>
@@ -52720,7 +52720,7 @@
       </c>
       <c r="S554" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T554" t="inlineStr"/>
@@ -52813,7 +52813,7 @@
       </c>
       <c r="S555" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T555" t="inlineStr"/>
@@ -52906,7 +52906,7 @@
       </c>
       <c r="S556" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T556" t="inlineStr"/>
@@ -52999,7 +52999,7 @@
       </c>
       <c r="S557" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T557" t="inlineStr"/>
@@ -53092,7 +53092,7 @@
       </c>
       <c r="S558" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T558" t="inlineStr"/>
@@ -53185,7 +53185,7 @@
       </c>
       <c r="S559" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T559" t="inlineStr"/>
@@ -53278,7 +53278,7 @@
       </c>
       <c r="S560" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T560" t="inlineStr"/>
@@ -53371,7 +53371,7 @@
       </c>
       <c r="S561" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T561" t="inlineStr"/>
@@ -53464,7 +53464,7 @@
       </c>
       <c r="S562" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T562" t="inlineStr"/>
@@ -53557,7 +53557,7 @@
       </c>
       <c r="S563" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T563" t="inlineStr"/>
@@ -53650,7 +53650,7 @@
       </c>
       <c r="S564" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T564" t="inlineStr"/>
@@ -53743,7 +53743,7 @@
       </c>
       <c r="S565" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T565" t="inlineStr"/>
@@ -53836,7 +53836,7 @@
       </c>
       <c r="S566" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T566" t="inlineStr"/>
@@ -53929,7 +53929,7 @@
       </c>
       <c r="S567" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T567" t="inlineStr"/>
@@ -54022,7 +54022,7 @@
       </c>
       <c r="S568" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T568" t="inlineStr"/>
@@ -54115,7 +54115,7 @@
       </c>
       <c r="S569" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T569" t="inlineStr"/>
@@ -54208,7 +54208,7 @@
       </c>
       <c r="S570" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T570" t="inlineStr"/>
@@ -54301,7 +54301,7 @@
       </c>
       <c r="S571" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T571" t="inlineStr"/>
@@ -54394,7 +54394,7 @@
       </c>
       <c r="S572" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T572" t="inlineStr"/>
@@ -54487,7 +54487,7 @@
       </c>
       <c r="S573" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T573" t="inlineStr"/>
@@ -54580,7 +54580,7 @@
       </c>
       <c r="S574" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T574" t="inlineStr"/>
@@ -54673,7 +54673,7 @@
       </c>
       <c r="S575" t="inlineStr">
         <is>
-          <t>17-01-2021 08:30</t>
+          <t>2021-01-17 08:30:00</t>
         </is>
       </c>
       <c r="T575" t="inlineStr"/>
@@ -54766,7 +54766,7 @@
       </c>
       <c r="S576" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T576" t="inlineStr"/>
@@ -54859,7 +54859,7 @@
       </c>
       <c r="S577" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T577" t="inlineStr"/>
@@ -54952,7 +54952,7 @@
       </c>
       <c r="S578" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T578" t="inlineStr"/>
@@ -55045,7 +55045,7 @@
       </c>
       <c r="S579" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T579" t="inlineStr"/>
@@ -55138,7 +55138,7 @@
       </c>
       <c r="S580" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T580" t="inlineStr"/>
@@ -55231,7 +55231,7 @@
       </c>
       <c r="S581" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T581" t="inlineStr"/>
@@ -55324,7 +55324,7 @@
       </c>
       <c r="S582" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T582" t="inlineStr"/>
@@ -55417,7 +55417,7 @@
       </c>
       <c r="S583" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T583" t="inlineStr"/>
@@ -55510,7 +55510,7 @@
       </c>
       <c r="S584" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T584" t="n">
@@ -55609,7 +55609,7 @@
       </c>
       <c r="S585" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T585" t="n">
@@ -55708,7 +55708,7 @@
       </c>
       <c r="S586" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T586" t="n">
@@ -55811,7 +55811,7 @@
       </c>
       <c r="S587" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T587" t="inlineStr"/>
@@ -55904,7 +55904,7 @@
       </c>
       <c r="S588" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T588" t="inlineStr"/>
@@ -55997,7 +55997,7 @@
       </c>
       <c r="S589" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T589" t="inlineStr"/>
@@ -56090,7 +56090,7 @@
       </c>
       <c r="S590" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T590" t="inlineStr"/>
@@ -56183,7 +56183,7 @@
       </c>
       <c r="S591" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T591" t="inlineStr"/>
@@ -56276,7 +56276,7 @@
       </c>
       <c r="S592" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T592" t="inlineStr"/>
@@ -56369,7 +56369,7 @@
       </c>
       <c r="S593" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T593" t="inlineStr"/>
@@ -56462,7 +56462,7 @@
       </c>
       <c r="S594" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T594" t="inlineStr"/>
@@ -56555,7 +56555,7 @@
       </c>
       <c r="S595" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T595" t="inlineStr"/>
@@ -56648,7 +56648,7 @@
       </c>
       <c r="S596" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T596" t="inlineStr"/>
@@ -56741,7 +56741,7 @@
       </c>
       <c r="S597" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T597" t="n">
@@ -56836,7 +56836,7 @@
       </c>
       <c r="S598" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T598" t="n">
@@ -56931,7 +56931,7 @@
       </c>
       <c r="S599" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T599" t="n">
@@ -57026,7 +57026,7 @@
       </c>
       <c r="S600" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T600" t="n">
@@ -57121,7 +57121,7 @@
       </c>
       <c r="S601" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T601" t="n">
@@ -57216,7 +57216,7 @@
       </c>
       <c r="S602" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T602" t="n">
@@ -57311,7 +57311,7 @@
       </c>
       <c r="S603" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T603" t="n">
@@ -57406,7 +57406,7 @@
       </c>
       <c r="S604" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T604" t="n">
@@ -57501,7 +57501,7 @@
       </c>
       <c r="S605" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T605" t="n">
@@ -57596,7 +57596,7 @@
       </c>
       <c r="S606" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T606" t="n">
@@ -57691,7 +57691,7 @@
       </c>
       <c r="S607" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T607" t="n">
@@ -57786,7 +57786,7 @@
       </c>
       <c r="S608" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T608" t="n">
@@ -57881,7 +57881,7 @@
       </c>
       <c r="S609" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T609" t="n">
@@ -57976,7 +57976,7 @@
       </c>
       <c r="S610" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T610" t="n">
@@ -58071,7 +58071,7 @@
       </c>
       <c r="S611" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T611" t="n">
@@ -58166,7 +58166,7 @@
       </c>
       <c r="S612" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T612" t="n">
@@ -58261,7 +58261,7 @@
       </c>
       <c r="S613" t="inlineStr">
         <is>
-          <t>08-05-2021 08:30</t>
+          <t>2021-08-05 08:30:00</t>
         </is>
       </c>
       <c r="T613" t="n">
@@ -58356,7 +58356,7 @@
       </c>
       <c r="S614" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T614" t="n">
@@ -58451,7 +58451,7 @@
       </c>
       <c r="S615" t="inlineStr">
         <is>
-          <t>09-07-2021 08:30</t>
+          <t>2021-09-07 08:30:00</t>
         </is>
       </c>
       <c r="T615" t="n">
@@ -58546,7 +58546,7 @@
       </c>
       <c r="S616" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T616" t="n">
@@ -58641,7 +58641,7 @@
       </c>
       <c r="S617" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T617" t="n">
@@ -58736,7 +58736,7 @@
       </c>
       <c r="S618" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T618" t="n">
@@ -58831,7 +58831,7 @@
       </c>
       <c r="S619" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T619" t="n">
@@ -58926,7 +58926,7 @@
       </c>
       <c r="S620" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T620" t="n">
@@ -59021,7 +59021,7 @@
       </c>
       <c r="S621" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T621" t="n">
@@ -59116,7 +59116,7 @@
       </c>
       <c r="S622" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T622" t="n">
@@ -59211,7 +59211,7 @@
       </c>
       <c r="S623" t="inlineStr">
         <is>
-          <t>30-07-2021 08:30</t>
+          <t>2021-07-30 08:30:00</t>
         </is>
       </c>
       <c r="T623" t="n">
@@ -59306,7 +59306,7 @@
       </c>
       <c r="S624" t="inlineStr">
         <is>
-          <t>25-08-2021 08:30</t>
+          <t>2021-08-25 08:30:00</t>
         </is>
       </c>
       <c r="T624" t="n">
@@ -59401,7 +59401,7 @@
       </c>
       <c r="S625" t="inlineStr">
         <is>
-          <t>23-09-2021 08:30</t>
+          <t>2021-09-23 08:30:00</t>
         </is>
       </c>
       <c r="T625" t="n">
@@ -59496,7 +59496,7 @@
       </c>
       <c r="S626" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T626" t="n">
@@ -59591,7 +59591,7 @@
       </c>
       <c r="S627" t="inlineStr">
         <is>
-          <t>28-12-2021 08:30</t>
+          <t>2021-12-28 08:30:00</t>
         </is>
       </c>
       <c r="T627" t="n">
@@ -59686,7 +59686,7 @@
       </c>
       <c r="S628" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T628" t="n">
@@ -59781,7 +59781,7 @@
       </c>
       <c r="S629" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T629" t="n">
@@ -59876,7 +59876,7 @@
       </c>
       <c r="S630" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T630" t="n">
@@ -59971,7 +59971,7 @@
       </c>
       <c r="S631" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T631" t="n">
@@ -60066,7 +60066,7 @@
       </c>
       <c r="S632" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T632" t="n">
@@ -60161,7 +60161,7 @@
       </c>
       <c r="S633" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T633" t="n">
@@ -60256,7 +60256,7 @@
       </c>
       <c r="S634" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T634" t="n">
@@ -60351,7 +60351,7 @@
       </c>
       <c r="S635" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T635" t="n">
@@ -60446,7 +60446,7 @@
       </c>
       <c r="S636" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T636" t="n">
@@ -60541,7 +60541,7 @@
       </c>
       <c r="S637" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T637" t="n">
@@ -60636,7 +60636,7 @@
       </c>
       <c r="S638" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T638" t="n">
@@ -60731,7 +60731,7 @@
       </c>
       <c r="S639" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T639" t="n">
@@ -60826,7 +60826,7 @@
       </c>
       <c r="S640" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T640" t="n">
@@ -60921,7 +60921,7 @@
       </c>
       <c r="S641" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T641" t="n">
@@ -61016,7 +61016,7 @@
       </c>
       <c r="S642" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T642" t="n">
@@ -61111,7 +61111,7 @@
       </c>
       <c r="S643" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T643" t="n">
@@ -61206,7 +61206,7 @@
       </c>
       <c r="S644" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T644" t="n">
@@ -61301,7 +61301,7 @@
       </c>
       <c r="S645" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T645" t="n">
@@ -61396,7 +61396,7 @@
       </c>
       <c r="S646" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T646" t="n">
@@ -61491,7 +61491,7 @@
       </c>
       <c r="S647" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T647" t="n">
@@ -61586,7 +61586,7 @@
       </c>
       <c r="S648" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T648" t="n">
@@ -61681,7 +61681,7 @@
       </c>
       <c r="S649" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T649" t="n">
@@ -61776,7 +61776,7 @@
       </c>
       <c r="S650" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T650" t="inlineStr"/>
@@ -61869,7 +61869,7 @@
       </c>
       <c r="S651" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T651" t="inlineStr"/>
@@ -61962,7 +61962,7 @@
       </c>
       <c r="S652" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T652" t="inlineStr"/>
@@ -62055,7 +62055,7 @@
       </c>
       <c r="S653" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T653" t="inlineStr"/>
@@ -62148,7 +62148,7 @@
       </c>
       <c r="S654" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T654" t="inlineStr"/>
@@ -62241,7 +62241,7 @@
       </c>
       <c r="S655" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T655" t="inlineStr"/>
@@ -62334,7 +62334,7 @@
       </c>
       <c r="S656" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T656" t="inlineStr"/>
@@ -62427,7 +62427,7 @@
       </c>
       <c r="S657" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T657" t="inlineStr"/>
@@ -62520,7 +62520,7 @@
       </c>
       <c r="S658" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T658" t="inlineStr"/>
@@ -62613,7 +62613,7 @@
       </c>
       <c r="S659" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T659" t="inlineStr"/>
@@ -62706,7 +62706,7 @@
       </c>
       <c r="S660" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T660" t="inlineStr"/>
@@ -62799,7 +62799,7 @@
       </c>
       <c r="S661" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T661" t="inlineStr"/>
@@ -62892,7 +62892,7 @@
       </c>
       <c r="S662" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T662" t="inlineStr"/>
@@ -62985,7 +62985,7 @@
       </c>
       <c r="S663" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T663" t="inlineStr"/>
@@ -63078,7 +63078,7 @@
       </c>
       <c r="S664" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T664" t="inlineStr"/>
@@ -63171,7 +63171,7 @@
       </c>
       <c r="S665" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T665" t="inlineStr"/>
@@ -63264,7 +63264,7 @@
       </c>
       <c r="S666" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T666" t="inlineStr"/>
@@ -63357,7 +63357,7 @@
       </c>
       <c r="S667" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T667" t="inlineStr"/>
@@ -63450,7 +63450,7 @@
       </c>
       <c r="S668" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T668" t="inlineStr"/>
@@ -63543,7 +63543,7 @@
       </c>
       <c r="S669" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T669" t="inlineStr"/>
@@ -63636,7 +63636,7 @@
       </c>
       <c r="S670" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T670" t="inlineStr"/>
@@ -63729,7 +63729,7 @@
       </c>
       <c r="S671" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T671" t="inlineStr"/>
@@ -63822,7 +63822,7 @@
       </c>
       <c r="S672" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T672" t="inlineStr"/>
@@ -63915,7 +63915,7 @@
       </c>
       <c r="S673" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T673" t="inlineStr"/>
@@ -64008,7 +64008,7 @@
       </c>
       <c r="S674" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T674" t="inlineStr"/>
@@ -64101,7 +64101,7 @@
       </c>
       <c r="S675" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T675" t="inlineStr"/>
@@ -64194,7 +64194,7 @@
       </c>
       <c r="S676" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T676" t="inlineStr"/>
@@ -64287,7 +64287,7 @@
       </c>
       <c r="S677" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T677" t="inlineStr"/>
@@ -64380,7 +64380,7 @@
       </c>
       <c r="S678" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T678" t="inlineStr"/>
@@ -64473,7 +64473,7 @@
       </c>
       <c r="S679" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T679" t="inlineStr"/>
@@ -64566,7 +64566,7 @@
       </c>
       <c r="S680" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T680" t="inlineStr"/>
@@ -64659,7 +64659,7 @@
       </c>
       <c r="S681" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T681" t="inlineStr"/>
@@ -64752,7 +64752,7 @@
       </c>
       <c r="S682" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T682" t="inlineStr"/>
@@ -64845,7 +64845,7 @@
       </c>
       <c r="S683" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T683" t="inlineStr"/>
@@ -64938,7 +64938,7 @@
       </c>
       <c r="S684" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T684" t="inlineStr"/>
@@ -65031,7 +65031,7 @@
       </c>
       <c r="S685" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T685" t="n">
@@ -65126,7 +65126,7 @@
       </c>
       <c r="S686" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T686" t="n">
@@ -65221,7 +65221,7 @@
       </c>
       <c r="S687" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T687" t="n">
@@ -65316,7 +65316,7 @@
       </c>
       <c r="S688" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T688" t="n">
@@ -65411,7 +65411,7 @@
       </c>
       <c r="S689" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T689" t="n">
@@ -65506,7 +65506,7 @@
       </c>
       <c r="S690" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T690" t="n">
@@ -65601,7 +65601,7 @@
       </c>
       <c r="S691" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T691" t="n">
@@ -65696,7 +65696,7 @@
       </c>
       <c r="S692" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T692" t="n">
@@ -65791,7 +65791,7 @@
       </c>
       <c r="S693" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T693" t="n">
@@ -65886,7 +65886,7 @@
       </c>
       <c r="S694" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T694" t="n">
@@ -65981,7 +65981,7 @@
       </c>
       <c r="S695" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T695" t="n">
@@ -66076,7 +66076,7 @@
       </c>
       <c r="S696" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T696" t="inlineStr"/>
@@ -66169,7 +66169,7 @@
       </c>
       <c r="S697" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T697" t="inlineStr"/>
@@ -66262,7 +66262,7 @@
       </c>
       <c r="S698" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T698" t="inlineStr"/>
@@ -66355,7 +66355,7 @@
       </c>
       <c r="S699" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T699" t="inlineStr"/>
@@ -66448,7 +66448,7 @@
       </c>
       <c r="S700" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T700" t="inlineStr"/>
@@ -66541,7 +66541,7 @@
       </c>
       <c r="S701" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T701" t="inlineStr"/>
@@ -66634,7 +66634,7 @@
       </c>
       <c r="S702" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T702" t="inlineStr"/>
@@ -66727,7 +66727,7 @@
       </c>
       <c r="S703" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T703" t="inlineStr"/>
@@ -66820,7 +66820,7 @@
       </c>
       <c r="S704" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T704" t="inlineStr"/>
@@ -66913,7 +66913,7 @@
       </c>
       <c r="S705" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T705" t="n">
@@ -67008,7 +67008,7 @@
       </c>
       <c r="S706" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T706" t="n">
@@ -67103,7 +67103,7 @@
       </c>
       <c r="S707" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T707" t="n">
@@ -67198,7 +67198,7 @@
       </c>
       <c r="S708" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T708" t="n">
@@ -67293,7 +67293,7 @@
       </c>
       <c r="S709" t="inlineStr">
         <is>
-          <t>08-05-2021 08:30</t>
+          <t>2021-08-05 08:30:00</t>
         </is>
       </c>
       <c r="T709" t="n">
@@ -67388,7 +67388,7 @@
       </c>
       <c r="S710" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T710" t="n">
@@ -67483,7 +67483,7 @@
       </c>
       <c r="S711" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T711" t="n">
@@ -67578,7 +67578,7 @@
       </c>
       <c r="S712" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T712" t="n">
@@ -67673,7 +67673,7 @@
       </c>
       <c r="S713" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T713" t="n">
@@ -67768,7 +67768,7 @@
       </c>
       <c r="S714" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T714" t="n">
@@ -67863,7 +67863,7 @@
       </c>
       <c r="S715" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T715" t="n">
@@ -67958,7 +67958,7 @@
       </c>
       <c r="S716" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T716" t="n">
@@ -68053,7 +68053,7 @@
       </c>
       <c r="S717" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T717" t="n">
@@ -68148,7 +68148,7 @@
       </c>
       <c r="S718" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T718" t="n">
@@ -68243,7 +68243,7 @@
       </c>
       <c r="S719" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T719" t="n">
@@ -68338,7 +68338,7 @@
       </c>
       <c r="S720" t="inlineStr">
         <is>
-          <t>27-07-2021 08:30</t>
+          <t>2021-07-27 08:30:00</t>
         </is>
       </c>
       <c r="T720" t="n">
@@ -68433,7 +68433,7 @@
       </c>
       <c r="S721" t="inlineStr">
         <is>
-          <t>28-08-2021 08:30</t>
+          <t>2021-08-28 08:30:00</t>
         </is>
       </c>
       <c r="T721" t="n">
@@ -68528,7 +68528,7 @@
       </c>
       <c r="S722" t="inlineStr">
         <is>
-          <t>19-09-2021 08:30</t>
+          <t>2021-09-19 08:30:00</t>
         </is>
       </c>
       <c r="T722" t="n">
@@ -68623,7 +68623,7 @@
       </c>
       <c r="S723" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T723" t="n">
@@ -68718,7 +68718,7 @@
       </c>
       <c r="S724" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T724" t="n">
@@ -68813,7 +68813,7 @@
       </c>
       <c r="S725" t="inlineStr">
         <is>
-          <t>31-12-2021 08:30</t>
+          <t>2021-12-31 08:30:00</t>
         </is>
       </c>
       <c r="T725" t="n">
@@ -68908,7 +68908,7 @@
       </c>
       <c r="S726" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T726" t="inlineStr"/>
@@ -69001,7 +69001,7 @@
       </c>
       <c r="S727" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T727" t="inlineStr"/>
@@ -69094,7 +69094,7 @@
       </c>
       <c r="S728" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T728" t="inlineStr"/>
@@ -69187,7 +69187,7 @@
       </c>
       <c r="S729" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T729" t="inlineStr"/>
@@ -69280,7 +69280,7 @@
       </c>
       <c r="S730" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T730" t="inlineStr"/>
@@ -69373,7 +69373,7 @@
       </c>
       <c r="S731" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T731" t="inlineStr"/>
@@ -69466,7 +69466,7 @@
       </c>
       <c r="S732" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T732" t="inlineStr"/>
@@ -69559,7 +69559,7 @@
       </c>
       <c r="S733" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T733" t="inlineStr"/>
@@ -69652,7 +69652,7 @@
       </c>
       <c r="S734" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T734" t="inlineStr"/>
@@ -69745,7 +69745,7 @@
       </c>
       <c r="S735" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T735" t="inlineStr"/>
@@ -69838,7 +69838,7 @@
       </c>
       <c r="S736" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T736" t="inlineStr"/>
@@ -69931,7 +69931,7 @@
       </c>
       <c r="S737" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T737" t="inlineStr"/>
@@ -70024,7 +70024,7 @@
       </c>
       <c r="S738" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T738" t="inlineStr"/>
@@ -70117,7 +70117,7 @@
       </c>
       <c r="S739" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T739" t="inlineStr"/>
@@ -70210,7 +70210,7 @@
       </c>
       <c r="S740" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T740" t="inlineStr"/>
@@ -70303,7 +70303,7 @@
       </c>
       <c r="S741" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T741" t="inlineStr"/>
@@ -70396,7 +70396,7 @@
       </c>
       <c r="S742" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T742" t="inlineStr"/>
@@ -70489,7 +70489,7 @@
       </c>
       <c r="S743" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T743" t="inlineStr"/>
@@ -70582,7 +70582,7 @@
       </c>
       <c r="S744" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T744" t="inlineStr"/>
@@ -70675,7 +70675,7 @@
       </c>
       <c r="S745" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T745" t="inlineStr"/>
@@ -70768,7 +70768,7 @@
       </c>
       <c r="S746" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T746" t="inlineStr"/>
@@ -70861,7 +70861,7 @@
       </c>
       <c r="S747" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T747" t="inlineStr"/>
@@ -70954,7 +70954,7 @@
       </c>
       <c r="S748" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T748" t="inlineStr"/>
@@ -71047,7 +71047,7 @@
       </c>
       <c r="S749" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T749" t="inlineStr"/>
@@ -71140,7 +71140,7 @@
       </c>
       <c r="S750" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T750" t="inlineStr"/>
@@ -71233,7 +71233,7 @@
       </c>
       <c r="S751" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T751" t="n">
@@ -71328,7 +71328,7 @@
       </c>
       <c r="S752" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T752" t="n">
@@ -71423,7 +71423,7 @@
       </c>
       <c r="S753" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T753" t="n">
@@ -71518,7 +71518,7 @@
       </c>
       <c r="S754" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T754" t="n">
@@ -71613,7 +71613,7 @@
       </c>
       <c r="S755" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T755" t="n">
@@ -71708,7 +71708,7 @@
       </c>
       <c r="S756" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T756" t="n">
@@ -71803,7 +71803,7 @@
       </c>
       <c r="S757" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T757" t="n">
@@ -71898,7 +71898,7 @@
       </c>
       <c r="S758" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T758" t="n">
@@ -71993,7 +71993,7 @@
       </c>
       <c r="S759" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T759" t="n">
@@ -72088,7 +72088,7 @@
       </c>
       <c r="S760" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T760" t="n">
@@ -72183,7 +72183,7 @@
       </c>
       <c r="S761" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T761" t="n">
@@ -72278,7 +72278,7 @@
       </c>
       <c r="S762" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T762" t="n">
@@ -72373,7 +72373,7 @@
       </c>
       <c r="S763" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T763" t="inlineStr"/>
@@ -72466,7 +72466,7 @@
       </c>
       <c r="S764" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T764" t="inlineStr"/>
@@ -72559,7 +72559,7 @@
       </c>
       <c r="S765" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T765" t="inlineStr"/>
@@ -72652,7 +72652,7 @@
       </c>
       <c r="S766" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T766" t="inlineStr"/>
@@ -72745,7 +72745,7 @@
       </c>
       <c r="S767" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T767" t="inlineStr"/>
@@ -72838,7 +72838,7 @@
       </c>
       <c r="S768" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T768" t="inlineStr"/>
@@ -72931,7 +72931,7 @@
       </c>
       <c r="S769" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T769" t="inlineStr"/>
@@ -73024,7 +73024,7 @@
       </c>
       <c r="S770" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T770" t="inlineStr"/>
@@ -73117,7 +73117,7 @@
       </c>
       <c r="S771" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T771" t="inlineStr"/>
@@ -73210,7 +73210,7 @@
       </c>
       <c r="S772" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T772" t="inlineStr"/>
@@ -73303,7 +73303,7 @@
       </c>
       <c r="S773" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T773" t="inlineStr"/>
@@ -73396,7 +73396,7 @@
       </c>
       <c r="S774" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T774" t="inlineStr"/>
@@ -73489,7 +73489,7 @@
       </c>
       <c r="S775" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T775" t="inlineStr"/>
@@ -73582,7 +73582,7 @@
       </c>
       <c r="S776" t="inlineStr">
         <is>
-          <t>11-04-2021 08:30</t>
+          <t>2021-11-04 08:30:00</t>
         </is>
       </c>
       <c r="T776" t="n">
@@ -73685,7 +73685,7 @@
       </c>
       <c r="S777" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T777" t="n">
@@ -73788,7 +73788,7 @@
       </c>
       <c r="S778" t="inlineStr">
         <is>
-          <t>11-04-2021 08:30</t>
+          <t>2021-11-04 08:30:00</t>
         </is>
       </c>
       <c r="T778" t="n">
@@ -73891,7 +73891,7 @@
       </c>
       <c r="S779" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T779" t="n">
@@ -73994,7 +73994,7 @@
       </c>
       <c r="S780" t="inlineStr">
         <is>
-          <t>28-04-2021 08:30</t>
+          <t>2021-04-28 08:30:00</t>
         </is>
       </c>
       <c r="T780" t="n">
@@ -74097,7 +74097,7 @@
       </c>
       <c r="S781" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T781" t="n">
@@ -74200,7 +74200,7 @@
       </c>
       <c r="S782" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T782" t="n">
@@ -74303,7 +74303,7 @@
       </c>
       <c r="S783" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T783" t="n">
@@ -74402,7 +74402,7 @@
       </c>
       <c r="S784" t="inlineStr">
         <is>
-          <t>30-04-2021 08:30</t>
+          <t>2021-04-30 08:30:00</t>
         </is>
       </c>
       <c r="T784" t="n">
@@ -74505,7 +74505,7 @@
       </c>
       <c r="S785" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T785" t="n">
@@ -74608,7 +74608,7 @@
       </c>
       <c r="S786" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T786" t="inlineStr"/>
@@ -74709,7 +74709,7 @@
       </c>
       <c r="S787" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T787" t="n">
@@ -74808,7 +74808,7 @@
       </c>
       <c r="S788" t="inlineStr">
         <is>
-          <t>25-04-2021 08:30</t>
+          <t>2021-04-25 08:30:00</t>
         </is>
       </c>
       <c r="T788" t="inlineStr"/>
@@ -74905,7 +74905,7 @@
       </c>
       <c r="S789" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T789" t="n">
@@ -75004,7 +75004,7 @@
       </c>
       <c r="S790" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T790" t="n">
@@ -75103,7 +75103,7 @@
       </c>
       <c r="S791" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T791" t="n">
@@ -75202,7 +75202,7 @@
       </c>
       <c r="S792" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T792" t="inlineStr"/>
@@ -75299,7 +75299,7 @@
       </c>
       <c r="S793" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T793" t="n">
@@ -75398,7 +75398,7 @@
       </c>
       <c r="S794" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T794" t="n">
@@ -75501,7 +75501,7 @@
       </c>
       <c r="S795" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T795" t="n">
@@ -75604,7 +75604,7 @@
       </c>
       <c r="S796" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T796" t="n">
@@ -75703,7 +75703,7 @@
       </c>
       <c r="S797" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T797" t="n">
@@ -75802,7 +75802,7 @@
       </c>
       <c r="S798" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T798" t="n">
@@ -75905,7 +75905,7 @@
       </c>
       <c r="S799" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T799" t="n">
@@ -76004,7 +76004,7 @@
       </c>
       <c r="S800" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T800" t="n">
@@ -76103,7 +76103,7 @@
       </c>
       <c r="S801" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T801" t="n">
@@ -76206,7 +76206,7 @@
       </c>
       <c r="S802" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T802" t="n">
@@ -76301,7 +76301,7 @@
       </c>
       <c r="S803" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T803" t="n">
@@ -76396,7 +76396,7 @@
       </c>
       <c r="S804" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T804" t="n">
@@ -76491,7 +76491,7 @@
       </c>
       <c r="S805" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T805" t="n">
@@ -76586,7 +76586,7 @@
       </c>
       <c r="S806" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T806" t="n">
@@ -76681,7 +76681,7 @@
       </c>
       <c r="S807" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T807" t="n">
@@ -76776,7 +76776,7 @@
       </c>
       <c r="S808" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T808" t="n">
@@ -76871,7 +76871,7 @@
       </c>
       <c r="S809" t="inlineStr">
         <is>
-          <t>29-09-2021 08:30</t>
+          <t>2021-09-29 08:30:00</t>
         </is>
       </c>
       <c r="T809" t="n">
@@ -76966,7 +76966,7 @@
       </c>
       <c r="S810" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T810" t="n">
@@ -77061,7 +77061,7 @@
       </c>
       <c r="S811" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T811" t="n">
@@ -77156,7 +77156,7 @@
       </c>
       <c r="S812" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T812" t="n">
@@ -77251,7 +77251,7 @@
       </c>
       <c r="S813" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T813" t="n">
@@ -77346,7 +77346,7 @@
       </c>
       <c r="S814" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T814" t="n">
@@ -77441,7 +77441,7 @@
       </c>
       <c r="S815" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T815" t="n">
@@ -77536,7 +77536,7 @@
       </c>
       <c r="S816" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T816" t="n">
@@ -77631,7 +77631,7 @@
       </c>
       <c r="S817" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T817" t="n">
@@ -77726,7 +77726,7 @@
       </c>
       <c r="S818" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T818" t="n">
@@ -77821,7 +77821,7 @@
       </c>
       <c r="S819" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T819" t="n">
@@ -77916,7 +77916,7 @@
       </c>
       <c r="S820" t="inlineStr">
         <is>
-          <t>29-09-2021 08:30</t>
+          <t>2021-09-29 08:30:00</t>
         </is>
       </c>
       <c r="T820" t="n">
@@ -78011,7 +78011,7 @@
       </c>
       <c r="S821" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T821" t="n">
@@ -78106,7 +78106,7 @@
       </c>
       <c r="S822" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T822" t="n">
@@ -78201,7 +78201,7 @@
       </c>
       <c r="S823" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T823" t="n">
@@ -78296,7 +78296,7 @@
       </c>
       <c r="S824" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T824" t="n">
@@ -78391,7 +78391,7 @@
       </c>
       <c r="S825" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T825" t="n">
@@ -78486,7 +78486,7 @@
       </c>
       <c r="S826" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T826" t="n">
@@ -78581,7 +78581,7 @@
       </c>
       <c r="S827" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T827" t="n">
@@ -78676,7 +78676,7 @@
       </c>
       <c r="S828" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T828" t="n">
@@ -78771,7 +78771,7 @@
       </c>
       <c r="S829" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T829" t="n">
@@ -78866,7 +78866,7 @@
       </c>
       <c r="S830" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T830" t="n">
@@ -78961,7 +78961,7 @@
       </c>
       <c r="S831" t="inlineStr">
         <is>
-          <t>29-09-2021 08:30</t>
+          <t>2021-09-29 08:30:00</t>
         </is>
       </c>
       <c r="T831" t="n">
@@ -79056,7 +79056,7 @@
       </c>
       <c r="S832" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T832" t="n">
@@ -79151,7 +79151,7 @@
       </c>
       <c r="S833" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T833" t="n">
@@ -79246,7 +79246,7 @@
       </c>
       <c r="S834" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T834" t="n">
@@ -79341,7 +79341,7 @@
       </c>
       <c r="S835" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T835" t="n">
@@ -79436,7 +79436,7 @@
       </c>
       <c r="S836" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T836" t="n">
@@ -79531,7 +79531,7 @@
       </c>
       <c r="S837" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T837" t="n">
@@ -79626,7 +79626,7 @@
       </c>
       <c r="S838" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T838" t="n">
@@ -79721,7 +79721,7 @@
       </c>
       <c r="S839" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T839" t="n">
@@ -79816,7 +79816,7 @@
       </c>
       <c r="S840" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T840" t="n">
@@ -79911,7 +79911,7 @@
       </c>
       <c r="S841" t="inlineStr">
         <is>
-          <t>12-08-2021 08:30</t>
+          <t>2021-12-08 08:30:00</t>
         </is>
       </c>
       <c r="T841" t="n">
@@ -80006,7 +80006,7 @@
       </c>
       <c r="S842" t="inlineStr">
         <is>
-          <t>29-09-2021 08:30</t>
+          <t>2021-09-29 08:30:00</t>
         </is>
       </c>
       <c r="T842" t="n">
@@ -80101,7 +80101,7 @@
       </c>
       <c r="S843" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T843" t="n">
@@ -80196,7 +80196,7 @@
       </c>
       <c r="S844" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T844" t="n">
@@ -80291,7 +80291,7 @@
       </c>
       <c r="S845" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T845" t="n">
@@ -80386,7 +80386,7 @@
       </c>
       <c r="S846" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T846" t="inlineStr"/>
@@ -80479,7 +80479,7 @@
       </c>
       <c r="S847" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T847" t="inlineStr"/>
@@ -80572,7 +80572,7 @@
       </c>
       <c r="S848" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T848" t="inlineStr"/>
@@ -80665,7 +80665,7 @@
       </c>
       <c r="S849" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T849" t="inlineStr"/>
@@ -80758,7 +80758,7 @@
       </c>
       <c r="S850" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T850" t="inlineStr"/>
@@ -80851,7 +80851,7 @@
       </c>
       <c r="S851" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T851" t="inlineStr"/>
@@ -80944,7 +80944,7 @@
       </c>
       <c r="S852" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T852" t="inlineStr"/>
@@ -81037,7 +81037,7 @@
       </c>
       <c r="S853" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T853" t="inlineStr"/>
@@ -81130,7 +81130,7 @@
       </c>
       <c r="S854" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T854" t="inlineStr"/>
@@ -81223,7 +81223,7 @@
       </c>
       <c r="S855" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T855" t="inlineStr"/>
@@ -81316,7 +81316,7 @@
       </c>
       <c r="S856" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T856" t="inlineStr"/>
@@ -81409,7 +81409,7 @@
       </c>
       <c r="S857" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T857" t="inlineStr"/>
@@ -81502,7 +81502,7 @@
       </c>
       <c r="S858" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T858" t="inlineStr"/>
@@ -81595,7 +81595,7 @@
       </c>
       <c r="S859" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T859" t="inlineStr"/>
@@ -81688,7 +81688,7 @@
       </c>
       <c r="S860" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T860" t="inlineStr"/>
@@ -81781,7 +81781,7 @@
       </c>
       <c r="S861" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T861" t="n">
@@ -81884,7 +81884,7 @@
       </c>
       <c r="S862" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T862" t="n">
@@ -81983,7 +81983,7 @@
       </c>
       <c r="S863" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T863" t="n">
@@ -82086,7 +82086,7 @@
       </c>
       <c r="S864" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T864" t="n">
@@ -82189,7 +82189,7 @@
       </c>
       <c r="S865" t="inlineStr">
         <is>
-          <t>27-12-2021 08:30</t>
+          <t>2021-12-27 08:30:00</t>
         </is>
       </c>
       <c r="T865" t="n">
@@ -82288,7 +82288,7 @@
       </c>
       <c r="S866" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T866" t="n">
@@ -82391,7 +82391,7 @@
       </c>
       <c r="S867" t="inlineStr">
         <is>
-          <t>29-10-2021 08:30</t>
+          <t>2021-10-29 08:30:00</t>
         </is>
       </c>
       <c r="T867" t="n">
@@ -82494,7 +82494,7 @@
       </c>
       <c r="S868" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T868" t="n">
@@ -82597,7 +82597,7 @@
       </c>
       <c r="S869" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T869" t="n">
@@ -82696,7 +82696,7 @@
       </c>
       <c r="S870" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T870" t="inlineStr"/>
@@ -82793,7 +82793,7 @@
       </c>
       <c r="S871" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T871" t="n">
@@ -82892,7 +82892,7 @@
       </c>
       <c r="S872" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T872" t="n">
@@ -82991,7 +82991,7 @@
       </c>
       <c r="S873" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T873" t="n">
@@ -83090,7 +83090,7 @@
       </c>
       <c r="S874" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T874" t="n">
@@ -83193,7 +83193,7 @@
       </c>
       <c r="S875" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T875" t="n">
@@ -83296,7 +83296,7 @@
       </c>
       <c r="S876" t="inlineStr">
         <is>
-          <t>18-04-2021 08:30</t>
+          <t>2021-04-18 08:30:00</t>
         </is>
       </c>
       <c r="T876" t="n">
@@ -83395,7 +83395,7 @@
       </c>
       <c r="S877" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T877" t="n">
@@ -83494,7 +83494,7 @@
       </c>
       <c r="S878" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T878" t="n">
@@ -83597,7 +83597,7 @@
       </c>
       <c r="S879" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T879" t="n">
@@ -83700,7 +83700,7 @@
       </c>
       <c r="S880" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T880" t="n">
@@ -83803,7 +83803,7 @@
       </c>
       <c r="S881" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T881" t="n">
@@ -83906,7 +83906,7 @@
       </c>
       <c r="S882" t="inlineStr">
         <is>
-          <t>21-11-2021 08:30</t>
+          <t>2021-11-21 08:30:00</t>
         </is>
       </c>
       <c r="T882" t="n">
@@ -84009,7 +84009,7 @@
       </c>
       <c r="S883" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T883" t="n">
@@ -84112,7 +84112,7 @@
       </c>
       <c r="S884" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T884" t="n">
@@ -84215,7 +84215,7 @@
       </c>
       <c r="S885" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T885" t="inlineStr"/>
@@ -84312,7 +84312,7 @@
       </c>
       <c r="S886" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T886" t="n">
@@ -84415,7 +84415,7 @@
       </c>
       <c r="S887" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T887" t="n">
@@ -84510,7 +84510,7 @@
       </c>
       <c r="S888" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T888" t="n">
@@ -84605,7 +84605,7 @@
       </c>
       <c r="S889" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T889" t="n">
@@ -84700,7 +84700,7 @@
       </c>
       <c r="S890" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T890" t="n">
@@ -84795,7 +84795,7 @@
       </c>
       <c r="S891" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T891" t="n">
@@ -84890,7 +84890,7 @@
       </c>
       <c r="S892" t="inlineStr">
         <is>
-          <t>14-06-2021 08:30</t>
+          <t>2021-06-14 08:30:00</t>
         </is>
       </c>
       <c r="T892" t="n">
@@ -84985,7 +84985,7 @@
       </c>
       <c r="S893" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T893" t="n">
@@ -85080,7 +85080,7 @@
       </c>
       <c r="S894" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T894" t="n">
@@ -85175,7 +85175,7 @@
       </c>
       <c r="S895" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T895" t="n">
@@ -85270,7 +85270,7 @@
       </c>
       <c r="S896" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T896" t="n">
@@ -85365,7 +85365,7 @@
       </c>
       <c r="S897" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T897" t="n">
@@ -85460,7 +85460,7 @@
       </c>
       <c r="S898" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T898" t="n">
